--- a/Attendee list AQC 1.xlsx
+++ b/Attendee list AQC 1.xlsx
@@ -2280,8 +2280,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" ns1:Ignorable="x14ac x16r2 xr">
+  <fonts count="10" ns2:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2414,13 +2414,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFFF6D01"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2624,11 +2624,11 @@
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <ns3:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <ns4:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
